--- a/data/trans_orig/P15E_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23510</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64726</t>
+          <t>64833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88709</t>
+          <t>88323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15E_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>27366</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20931</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>25604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>16409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>70528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74045</t>
+          <t>81785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
